--- a/docs/oc-regiones/mobiliario-general-escolar-y-clinico/region-de-magallanes-y-de-la-antartica.xlsx
+++ b/docs/oc-regiones/mobiliario-general-escolar-y-clinico/region-de-magallanes-y-de-la-antartica.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,27 +514,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1776-54-CM26</t>
+          <t>1776-53-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
+          <t>Ortopedic</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>77.018.060-0</t>
+          <t>77.765.630-9</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,43 +569,43 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>18264.71</v>
+        <v>5816.99</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5394-477-CM26</t>
+          <t>1116007-73-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>71.133.700-8</t>
+          <t>61.104.000-8</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE MAGALLANES</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -630,6 +630,250 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
+        <v>24753.51</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1233613-1467-CM25</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2239-3-LR23</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>61.980.960-2</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Servicio Local de Educación Pública Magallanes</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Región de Magallanes y de la Antártica</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>77.018.060-0</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>20548.93</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2348-1542-CM25</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2239-3-LR23</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>69.250.200-0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUNTA ARENAS</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Región de Magallanes y de la Antártica</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>77.018.060-0</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>13199.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1776-54-CM26</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>60.804.017-K</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Región de Magallanes y de la Antártica</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>77.018.060-0</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>18264.71</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>5394-477-CM26</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>71.133.700-8</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE MAGALLANES</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Región de Magallanes y de la Antártica</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>LEFI SPA</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>77.324.357-3</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="n">
         <v>16109.89</v>
       </c>
     </row>
